--- a/src/main/resources/PotentialReviewersContact_Field_Values.xlsx
+++ b/src/main/resources/PotentialReviewersContact_Field_Values.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deepika\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB5019B-8357-4CA6-92A2-52B3111B773B}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF5F2D9-4358-44B5-8E5B-8B5C13D24AD6}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{FE4041C9-411E-47B8-A648-17C164901997}"/>
+    <workbookView xWindow="5928" yWindow="2928" windowWidth="17280" windowHeight="8964" activeTab="1" xr2:uid="{FE4041C9-411E-47B8-A648-17C164901997}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
+    <sheet name="Edition" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -61,6 +62,21 @@
   </si>
   <si>
     <t>None</t>
+  </si>
+  <si>
+    <t>Overview</t>
+  </si>
+  <si>
+    <t>Salutation</t>
+  </si>
+  <si>
+    <t>Mr.</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>987-456-8909</t>
   </si>
 </sst>
 </file>
@@ -481,4 +497,47 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59E2E7FA-17F4-4778-9079-BE9B528B7489}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/main/resources/PotentialReviewersContact_Field_Values.xlsx
+++ b/src/main/resources/PotentialReviewersContact_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21601"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF5F2D9-4358-44B5-8E5B-8B5C13D24AD6}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8591E05-22CE-40EF-9503-DC4B7F2D39D1}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5928" yWindow="2928" windowWidth="17280" windowHeight="8964" activeTab="1" xr2:uid="{FE4041C9-411E-47B8-A648-17C164901997}"/>
+    <workbookView xWindow="1500" yWindow="1500" windowWidth="17280" windowHeight="8964" activeTab="1" xr2:uid="{FE4041C9-411E-47B8-A648-17C164901997}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -52,15 +52,6 @@
     <t>Email</t>
   </si>
   <si>
-    <t>Staci</t>
-  </si>
-  <si>
-    <t>Alley</t>
-  </si>
-  <si>
-    <t>staci.alley@yopmail.com</t>
-  </si>
-  <si>
     <t>None</t>
   </si>
   <si>
@@ -77,6 +68,18 @@
   </si>
   <si>
     <t>987-456-8909</t>
+  </si>
+  <si>
+    <t>Automation</t>
+  </si>
+  <si>
+    <t>SME</t>
+  </si>
+  <si>
+    <t>automation.sme@yopmail.com</t>
+  </si>
+  <si>
+    <t>786-908-(5678)</t>
   </si>
 </sst>
 </file>
@@ -439,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72DA656C-1C51-41DB-AF9C-4CA03E90FA41}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.21875" bestFit="1" customWidth="1"/>
@@ -460,35 +463,46 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -517,24 +531,24 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/PotentialReviewersContact_Field_Values.xlsx
+++ b/src/main/resources/PotentialReviewersContact_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21901"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8591E05-22CE-40EF-9503-DC4B7F2D39D1}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59C1491E-9A2F-478C-B0D3-8FE7DB561749}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1500" windowWidth="17280" windowHeight="8964" activeTab="1" xr2:uid="{FE4041C9-411E-47B8-A648-17C164901997}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{FE4041C9-411E-47B8-A648-17C164901997}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>

--- a/src/main/resources/PotentialReviewersContact_Field_Values.xlsx
+++ b/src/main/resources/PotentialReviewersContact_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21901"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59C1491E-9A2F-478C-B0D3-8FE7DB561749}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA93F06D-354A-4EF7-AD5E-DAA16DF1DC94}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{FE4041C9-411E-47B8-A648-17C164901997}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{FE4041C9-411E-47B8-A648-17C164901997}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="14">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -56,12 +56,6 @@
   </si>
   <si>
     <t>Overview</t>
-  </si>
-  <si>
-    <t>Salutation</t>
-  </si>
-  <si>
-    <t>Mr.</t>
   </si>
   <si>
     <t>Phone</t>
@@ -469,7 +463,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -480,7 +474,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -491,7 +485,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -499,10 +493,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -515,7 +509,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59E2E7FA-17F4-4778-9079-BE9B528B7489}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -540,17 +534,6 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/main/resources/PotentialReviewersContact_Field_Values.xlsx
+++ b/src/main/resources/PotentialReviewersContact_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA93F06D-354A-4EF7-AD5E-DAA16DF1DC94}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{180CD74C-A411-41B9-9C35-D3D8756107FC}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{FE4041C9-411E-47B8-A648-17C164901997}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -53,9 +53,6 @@
   </si>
   <si>
     <t>None</t>
-  </si>
-  <si>
-    <t>Overview</t>
   </si>
   <si>
     <t>Phone</t>
@@ -463,7 +460,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -474,7 +471,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -485,7 +482,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -493,10 +490,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -511,6 +508,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59E2E7FA-17F4-4778-9079-BE9B528B7489}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -525,13 +525,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/PotentialReviewersContact_Field_Values.xlsx
+++ b/src/main/resources/PotentialReviewersContact_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{180CD74C-A411-41B9-9C35-D3D8756107FC}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ED5DC51-F1DD-46AF-A287-24B3849EE578}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{FE4041C9-411E-47B8-A648-17C164901997}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{FE4041C9-411E-47B8-A648-17C164901997}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -61,16 +61,16 @@
     <t>987-456-8909</t>
   </si>
   <si>
-    <t>Automation</t>
-  </si>
-  <si>
-    <t>SME</t>
-  </si>
-  <si>
     <t>automation.sme@yopmail.com</t>
   </si>
   <si>
     <t>786-908-(5678)</t>
+  </si>
+  <si>
+    <t>Automation Runtime</t>
+  </si>
+  <si>
+    <t>Contact</t>
   </si>
 </sst>
 </file>
@@ -460,7 +460,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -471,7 +471,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -482,7 +482,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -493,7 +493,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/PotentialReviewersContact_Field_Values.xlsx
+++ b/src/main/resources/PotentialReviewersContact_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22624"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MCPL#L92\Desktop\Automation projects\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ED5DC51-F1DD-46AF-A287-24B3849EE578}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF591A0D-B43D-477C-AF23-1C4A893A5224}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{FE4041C9-411E-47B8-A648-17C164901997}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11949" xr2:uid="{FE4041C9-411E-47B8-A648-17C164901997}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -67,10 +67,10 @@
     <t>786-908-(5678)</t>
   </si>
   <si>
-    <t>Automation Runtime</t>
-  </si>
-  <si>
     <t>Contact</t>
+  </si>
+  <si>
+    <t>Automation Runtime Contact</t>
   </si>
 </sst>
 </file>
@@ -434,14 +434,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72DA656C-1C51-41DB-AF9C-4CA03E90FA41}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="26.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.23046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.23046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -452,7 +452,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -460,10 +460,10 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -471,10 +471,10 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -485,7 +485,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -507,12 +507,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59E2E7FA-17F4-4778-9079-BE9B528B7489}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -523,7 +523,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>6</v>
       </c>

--- a/src/main/resources/PotentialReviewersContact_Field_Values.xlsx
+++ b/src/main/resources/PotentialReviewersContact_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22624"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25128"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MCPL#L92\Desktop\Automation projects\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF591A0D-B43D-477C-AF23-1C4A893A5224}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9B0A6B4-2FD8-455A-AB99-56DE18E51AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11949" xr2:uid="{FE4041C9-411E-47B8-A648-17C164901997}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{FE4041C9-411E-47B8-A648-17C164901997}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -61,9 +61,6 @@
     <t>987-456-8909</t>
   </si>
   <si>
-    <t>automation.sme@yopmail.com</t>
-  </si>
-  <si>
     <t>786-908-(5678)</t>
   </si>
   <si>
@@ -71,6 +68,9 @@
   </si>
   <si>
     <t>Automation Runtime Contact</t>
+  </si>
+  <si>
+    <t>automation.sme143@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -434,14 +434,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72DA656C-1C51-41DB-AF9C-4CA03E90FA41}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.23046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.23046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -452,7 +452,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -460,10 +460,10 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -471,10 +471,10 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -482,10 +482,10 @@
         <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -493,7 +493,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -507,12 +507,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59E2E7FA-17F4-4778-9079-BE9B528B7489}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -523,7 +523,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>

--- a/src/main/resources/PotentialReviewersContact_Field_Values.xlsx
+++ b/src/main/resources/PotentialReviewersContact_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25427"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9B0A6B4-2FD8-455A-AB99-56DE18E51AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E283106-D04C-453C-ADAD-C1658347B866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{FE4041C9-411E-47B8-A648-17C164901997}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{FE4041C9-411E-47B8-A648-17C164901997}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="28">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -58,9 +58,6 @@
     <t>Phone</t>
   </si>
   <si>
-    <t>987-456-8909</t>
-  </si>
-  <si>
     <t>786-908-(5678)</t>
   </si>
   <si>
@@ -71,13 +68,61 @@
   </si>
   <si>
     <t>automation.sme143@yopmail.com</t>
+  </si>
+  <si>
+    <t>fieldExternalReviewerAddress1__c</t>
+  </si>
+  <si>
+    <t>Street 1</t>
+  </si>
+  <si>
+    <t>fieldExternalReviewerCity__c</t>
+  </si>
+  <si>
+    <t>VA</t>
+  </si>
+  <si>
+    <t>fieldStateDropdownList__c</t>
+  </si>
+  <si>
+    <t>PA</t>
+  </si>
+  <si>
+    <t>fieldExternalReviewerZipCode__c</t>
+  </si>
+  <si>
+    <t>fieldAffiliatedInstitution__c</t>
+  </si>
+  <si>
+    <t>Automation testing</t>
+  </si>
+  <si>
+    <t>fieldExternalReviewerEducation__c</t>
+  </si>
+  <si>
+    <t>Automation Engineer</t>
+  </si>
+  <si>
+    <t>fieldExternalReviewerProfileDescription__c</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>fieldPrimaryAreaOfExpertisePicklist__c</t>
+  </si>
+  <si>
+    <t>Ambulatory Care Programs</t>
+  </si>
+  <si>
+    <t>fieldPrimaryAreaOfExpertise__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -92,6 +137,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF202124"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -115,9 +166,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -460,7 +512,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -471,7 +523,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -482,7 +534,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -493,7 +545,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -506,10 +558,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59E2E7FA-17F4-4778-9079-BE9B528B7489}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -527,11 +580,99 @@
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
-        <v>7</v>
+      <c r="B2" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
